--- a/data/inputs/details.xlsx
+++ b/data/inputs/details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utkarsh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921A7B66-A899-42CB-97B7-C46CA34035B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB430669-540E-4C02-938F-17EF08AB4E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="101">
   <si>
     <t>CITY</t>
   </si>
@@ -323,522 +323,6 @@
   </si>
   <si>
     <t>BLR-DRY-MH-Sumadhura2</t>
-  </si>
-  <si>
-    <t>BLR-MYLAPURA MH</t>
-  </si>
-  <si>
-    <t>BLR-Nelamangala-DRYMH</t>
-  </si>
-  <si>
-    <t>Chennai</t>
-  </si>
-  <si>
-    <t>CHN-DRY MH</t>
-  </si>
-  <si>
-    <t>CHN-DRY-MH2-THIRUVALLUR</t>
-  </si>
-  <si>
-    <t>BLR-Nagondanahalli</t>
-  </si>
-  <si>
-    <t>BLR-Bellandur-5</t>
-  </si>
-  <si>
-    <t>BLR-BASAVANAPURA</t>
-  </si>
-  <si>
-    <t>BLR-Kudlu</t>
-  </si>
-  <si>
-    <t>BLR-Sarjapur-2</t>
-  </si>
-  <si>
-    <t>BLR-BELLANDUR - 2</t>
-  </si>
-  <si>
-    <t>BLR-Carmelaram</t>
-  </si>
-  <si>
-    <t>BLR-Sarjapur New</t>
-  </si>
-  <si>
-    <t>BLR-Kadarenahalli</t>
-  </si>
-  <si>
-    <t>BLR-HSR-2</t>
-  </si>
-  <si>
-    <t>BLR-Neo Town</t>
-  </si>
-  <si>
-    <t>BLR-RAGHAVENDRA LAYOUT NETWORK 2</t>
-  </si>
-  <si>
-    <t>BLR-BTM-3</t>
-  </si>
-  <si>
-    <t>BLR-CV Raman Nagar Network</t>
-  </si>
-  <si>
-    <t>BLR-Kasavanahalli</t>
-  </si>
-  <si>
-    <t>BLR-Manjunatha layout</t>
-  </si>
-  <si>
-    <t>BLR-BELLANDUR-4</t>
-  </si>
-  <si>
-    <t>BLR-Agrahara Road</t>
-  </si>
-  <si>
-    <t>BLR-Electronic City Network-2</t>
-  </si>
-  <si>
-    <t>BLR-ITPL Layout</t>
-  </si>
-  <si>
-    <t>BLR-Sunrise Layout</t>
-  </si>
-  <si>
-    <t>BLR-Bellandur new</t>
-  </si>
-  <si>
-    <t>BLR-Michael Palaya</t>
-  </si>
-  <si>
-    <t>BLR-New Gurappanya Palya</t>
-  </si>
-  <si>
-    <t>BLR-Teachers colony</t>
-  </si>
-  <si>
-    <t>BLR-Choodasandra</t>
-  </si>
-  <si>
-    <t>BLR-Junnasandra</t>
-  </si>
-  <si>
-    <t>BLR-Bommasandra</t>
-  </si>
-  <si>
-    <t>BLR-Singasandra Network</t>
-  </si>
-  <si>
-    <t>BLR-Silver County</t>
-  </si>
-  <si>
-    <t>BLR-Brookfield Network</t>
-  </si>
-  <si>
-    <t>BLR-BTM Layout Network-3</t>
-  </si>
-  <si>
-    <t>BLR-Channasandra</t>
-  </si>
-  <si>
-    <t>BLR-Whitefield Network-2</t>
-  </si>
-  <si>
-    <t>BLR-Sompura</t>
-  </si>
-  <si>
-    <t>BLR-Silicon Town</t>
-  </si>
-  <si>
-    <t>BLR-Hope Farm New</t>
-  </si>
-  <si>
-    <t>BLR-Marathahalli-4</t>
-  </si>
-  <si>
-    <t>BLR-Bellandur-3</t>
-  </si>
-  <si>
-    <t>BLR-Basavanapura Network</t>
-  </si>
-  <si>
-    <t>BLR-Arekere</t>
-  </si>
-  <si>
-    <t>BLR-CV Raman Nagar Network-2</t>
-  </si>
-  <si>
-    <t>BLR-27th Main Road</t>
-  </si>
-  <si>
-    <t>BLR-Peenya Network</t>
-  </si>
-  <si>
-    <t>BLR-TMC Layout</t>
-  </si>
-  <si>
-    <t>BLR-Doddakannelli</t>
-  </si>
-  <si>
-    <t>BLR-Mico Layout Network</t>
-  </si>
-  <si>
-    <t>BLR-Devasandra Extension</t>
-  </si>
-  <si>
-    <t>BLR-Chandapura</t>
-  </si>
-  <si>
-    <t>BLR-Mico layout New</t>
-  </si>
-  <si>
-    <t>BLR-Bellandur 6</t>
-  </si>
-  <si>
-    <t>BLR-SINGASANDRA</t>
-  </si>
-  <si>
-    <t>BLR-Thyagaraja Nagar</t>
-  </si>
-  <si>
-    <t>BLR-Chamrajpet</t>
-  </si>
-  <si>
-    <t>BLR-Pipeline road new</t>
-  </si>
-  <si>
-    <t>BLR-Vijay Nagar Network</t>
-  </si>
-  <si>
-    <t>BLR- Sonnenahalli New</t>
-  </si>
-  <si>
-    <t>BLR-BEML Layout</t>
-  </si>
-  <si>
-    <t>BLR-Anjanapura</t>
-  </si>
-  <si>
-    <t>BLR-Ullal</t>
-  </si>
-  <si>
-    <t>BLR-Peenya New</t>
-  </si>
-  <si>
-    <t>BLR-Kengeri</t>
-  </si>
-  <si>
-    <t>BLR-Avalahalli Main</t>
-  </si>
-  <si>
-    <t>BLR-YESHWANTPUR</t>
-  </si>
-  <si>
-    <t>BLR-Kambipura</t>
-  </si>
-  <si>
-    <t>BLR-Malagala</t>
-  </si>
-  <si>
-    <t>BLR-Yelenahalli</t>
-  </si>
-  <si>
-    <t>BLR-RAGHAVENDRA LAYOUT</t>
-  </si>
-  <si>
-    <t>BLR-Kumaraswamy Layout</t>
-  </si>
-  <si>
-    <t>BLR-JAYANAGAR New</t>
-  </si>
-  <si>
-    <t>BLR-Banashankari Network</t>
-  </si>
-  <si>
-    <t>BLR-Electronic city network</t>
-  </si>
-  <si>
-    <t>BLR-Bagalakunte</t>
-  </si>
-  <si>
-    <t>BLR-Bannerghatta Network</t>
-  </si>
-  <si>
-    <t>BLR-Golahalli</t>
-  </si>
-  <si>
-    <t>BLR-RAGHAVENDRA LAYOUT NETWORK</t>
-  </si>
-  <si>
-    <t>BLR-RR Nagar Network</t>
-  </si>
-  <si>
-    <t>CHN-Ayanavaram</t>
-  </si>
-  <si>
-    <t>CHN-Sivan Nagar</t>
-  </si>
-  <si>
-    <t>CHN-Vyasarpadi</t>
-  </si>
-  <si>
-    <t>CHN-Mylapore Network-2</t>
-  </si>
-  <si>
-    <t>CHN-Velachery New</t>
-  </si>
-  <si>
-    <t>CHN-Thoraipakkam New</t>
-  </si>
-  <si>
-    <t>CHN-Elcot SEZ</t>
-  </si>
-  <si>
-    <t>CHN-Medavakkam Network</t>
-  </si>
-  <si>
-    <t>CHN-Nolambur</t>
-  </si>
-  <si>
-    <t>CHN-Navalur New</t>
-  </si>
-  <si>
-    <t>CHN-Parrys</t>
-  </si>
-  <si>
-    <t>CHN-TNAGAR NEW</t>
-  </si>
-  <si>
-    <t>CHN-Nanganallur Network</t>
-  </si>
-  <si>
-    <t>CHN-Puthagram</t>
-  </si>
-  <si>
-    <t>CHN-TNAGAR Network</t>
-  </si>
-  <si>
-    <t>CHN-PERAMBUR NEW</t>
-  </si>
-  <si>
-    <t>CHN-VGM Street</t>
-  </si>
-  <si>
-    <t>CHN-AMBATTUR</t>
-  </si>
-  <si>
-    <t>CHN-Porur</t>
-  </si>
-  <si>
-    <t>CHN-KK Nagar Network New</t>
-  </si>
-  <si>
-    <t>CHN-TNHB Layout</t>
-  </si>
-  <si>
-    <t>CHN-Mylapore Network</t>
-  </si>
-  <si>
-    <t>CHN-Anna Nagar New</t>
-  </si>
-  <si>
-    <t>CHN-KELAMBAKKAM New</t>
-  </si>
-  <si>
-    <t>CHN-Kelambakkam Network</t>
-  </si>
-  <si>
-    <t>CHN-OTTERI</t>
-  </si>
-  <si>
-    <t>CHN-Anna Nagar Network</t>
-  </si>
-  <si>
-    <t>CHN-Sathyavani</t>
-  </si>
-  <si>
-    <t>CHN-Nandambakam New</t>
-  </si>
-  <si>
-    <t>CHN-Saidapet</t>
-  </si>
-  <si>
-    <t>CHN-ECR</t>
-  </si>
-  <si>
-    <t>CHN-Villivakkam</t>
-  </si>
-  <si>
-    <t>CHN-Mogappair Network</t>
-  </si>
-  <si>
-    <t>CHN-Palavanthangal</t>
-  </si>
-  <si>
-    <t>CHN-Pammal new</t>
-  </si>
-  <si>
-    <t>CHN-Madambakkam Network-2</t>
-  </si>
-  <si>
-    <t>CHN-Mahindra World City</t>
-  </si>
-  <si>
-    <t>CHN-Maraimalai Nagar</t>
-  </si>
-  <si>
-    <t>CHN-Thirunagar</t>
-  </si>
-  <si>
-    <t>CHN-Mogappair New</t>
-  </si>
-  <si>
-    <t>CHN-Vanagram</t>
-  </si>
-  <si>
-    <t>CHN-Perumbakkam Network</t>
-  </si>
-  <si>
-    <t>CHN-Govarthanagiri</t>
-  </si>
-  <si>
-    <t>CHN-Mudichur Network</t>
-  </si>
-  <si>
-    <t>CHN-Kovilambakkam</t>
-  </si>
-  <si>
-    <t>CHN-PALLAVARAM</t>
-  </si>
-  <si>
-    <t>CHN-Perungudi</t>
-  </si>
-  <si>
-    <t>CHN-Guduvancheri</t>
-  </si>
-  <si>
-    <t>CHN-Santosh Nagar</t>
-  </si>
-  <si>
-    <t>CHN-KK Thazhai</t>
-  </si>
-  <si>
-    <t>CHN-CHITLAPAKKAM</t>
-  </si>
-  <si>
-    <t>CHN-Pammal Network 2</t>
-  </si>
-  <si>
-    <t>CHN-Sothupakkam</t>
-  </si>
-  <si>
-    <t>CHN-Selaiyur</t>
-  </si>
-  <si>
-    <t>TAMBARAM</t>
-  </si>
-  <si>
-    <t>CHN-Guduvancheri lake</t>
-  </si>
-  <si>
-    <t>CHN-Sithalapakkam</t>
-  </si>
-  <si>
-    <t>CHN-ADYAR NETWORK</t>
-  </si>
-  <si>
-    <t>CHN-GERUGAMBAKKAM NETWORK</t>
-  </si>
-  <si>
-    <t>CHN-Nanganallur New</t>
-  </si>
-  <si>
-    <t>CHN-Moolakazhani</t>
-  </si>
-  <si>
-    <t>CHN-Navalur Network</t>
-  </si>
-  <si>
-    <t>CHENNAI-MYLAPORE</t>
-  </si>
-  <si>
-    <t>CHN-Ashok Nagar</t>
-  </si>
-  <si>
-    <t>CHN-KKNAGAR NEW</t>
-  </si>
-  <si>
-    <t>CHN-Sakthi Avenue</t>
-  </si>
-  <si>
-    <t>CHN-Narayanapuram</t>
-  </si>
-  <si>
-    <t>CHN-Manivakkam</t>
-  </si>
-  <si>
-    <t>CHN-Thazhambur</t>
-  </si>
-  <si>
-    <t>CHN-Mount Road</t>
-  </si>
-  <si>
-    <t>CHN-Anakaputhur</t>
-  </si>
-  <si>
-    <t>CHN-Kolathur</t>
-  </si>
-  <si>
-    <t>CHN-VANDALUR NETWORK</t>
-  </si>
-  <si>
-    <t>CHN-Nungambakkam new</t>
-  </si>
-  <si>
-    <t>MADAMBAKKAM</t>
-  </si>
-  <si>
-    <t>CHN-Chromepet</t>
-  </si>
-  <si>
-    <t>CHN-Madhanandapuram</t>
-  </si>
-  <si>
-    <t>CHN-Sholinganallur New</t>
-  </si>
-  <si>
-    <t>CHN-Ambattur Network</t>
-  </si>
-  <si>
-    <t>CHN-VANDALUR</t>
-  </si>
-  <si>
-    <t>CHN-Avadi</t>
-  </si>
-  <si>
-    <t>CHN-Tirumudivakkam</t>
-  </si>
-  <si>
-    <t>CHN-KKR Nagar</t>
-  </si>
-  <si>
-    <t>CHN-ADYAR</t>
-  </si>
-  <si>
-    <t>CHN-Iyyappanthangal</t>
-  </si>
-  <si>
-    <t>CHN-KUMANANCHAVADI</t>
-  </si>
-  <si>
-    <t>CHN-Irumbuliyur</t>
-  </si>
-  <si>
-    <t>CHN-Velachery Network</t>
-  </si>
-  <si>
-    <t>CHN-KK Nagar Network-2</t>
-  </si>
-  <si>
-    <t>8FT_TRUCK</t>
   </si>
 </sst>
 </file>
@@ -1205,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E349"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
@@ -4225,2930 +3709,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D178" s="2">
-        <v>5478</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D179" s="2">
-        <v>6766</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D180" s="2">
-        <v>6508</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D181" s="2">
-        <v>9514</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D182" s="2">
-        <v>9232</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D183" s="2">
-        <v>7426</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D184" s="2">
-        <v>7098</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D185" s="2">
-        <v>8009</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D186" s="2">
-        <v>10093</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D187" s="2">
-        <v>6552</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D188" s="2">
-        <v>5246</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D189" s="2">
-        <v>4658</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D190" s="2">
-        <v>7594</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D191" s="2">
-        <v>10176</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D192" s="2">
-        <v>4862</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D193" s="2">
-        <v>6318</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D194" s="2">
-        <v>6850</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D195" s="2">
-        <v>6153</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D196" s="2">
-        <v>8070</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D197" s="2">
-        <v>9804</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D198" s="2">
-        <v>3891</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D199" s="2">
-        <v>8752</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D200" s="2">
-        <v>6446</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D201" s="2">
-        <v>6859</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D202" s="2">
-        <v>8410</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D203" s="2">
-        <v>6893</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D204" s="2">
-        <v>5395</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D205" s="2">
-        <v>7255</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D206" s="2">
-        <v>7095</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D207" s="2">
-        <v>5582</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D208" s="2">
-        <v>7625</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D209" s="2">
-        <v>12483</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D210" s="2">
-        <v>4471</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D211" s="2">
-        <v>10077</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D212" s="2">
-        <v>4997</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D213" s="2">
-        <v>8185</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D214" s="2">
-        <v>9287</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D215" s="2">
-        <v>8000</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D216" s="2">
-        <v>6616</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D217" s="2">
-        <v>6810</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D218" s="2">
-        <v>5864</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D219" s="2">
-        <v>8133</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D220" s="2">
-        <v>4725</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D221" s="2">
-        <v>3717</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D222" s="2">
-        <v>7150</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D223" s="2">
-        <v>6211</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D224" s="2">
-        <v>6576</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D225" s="2">
-        <v>1266</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D226" s="2">
-        <v>7358</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D227" s="2">
-        <v>7271</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D228" s="2">
-        <v>6642</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D229" s="2">
-        <v>5540</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D230" s="2">
-        <v>9381</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D231" s="2">
-        <v>7179</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D232" s="2">
-        <v>3791</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D233" s="2">
-        <v>9676</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D234" s="2">
-        <v>7720</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D235" s="2">
-        <v>9290</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D236" s="2">
-        <v>1182</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D237" s="2">
-        <v>6962</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D238" s="2">
-        <v>8482</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D239" s="2">
-        <v>8447</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D240" s="2">
-        <v>5311</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D241" s="2">
-        <v>8334</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D242" s="2">
-        <v>4015</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D243" s="2">
-        <v>5897</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D244" s="2">
-        <v>8650</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D245" s="2">
-        <v>3605</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D246" s="2">
-        <v>4863</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D247" s="2">
-        <v>7083</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D248" s="2">
-        <v>4722</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D249" s="2">
-        <v>8560</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D250" s="2">
-        <v>8423</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D251" s="2">
-        <v>7640</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D252" s="2">
-        <v>5549</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D253" s="2">
-        <v>5448</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D254" s="2">
-        <v>5214</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D255" s="2">
-        <v>10078</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D256" s="2">
-        <v>6501</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D257" s="2">
-        <v>7836</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D258" s="2">
-        <v>7061</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D259" s="2">
-        <v>6044</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D260" s="2">
-        <v>10333</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D261" s="2">
-        <v>3947</v>
-      </c>
-      <c r="E261" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D262" s="2">
-        <v>2249</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D263" s="2">
-        <v>7917</v>
-      </c>
-      <c r="E263" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D264" s="2">
-        <v>5956</v>
-      </c>
-      <c r="E264" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D265" s="2">
-        <v>10683</v>
-      </c>
-      <c r="E265" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D266" s="2">
-        <v>8889</v>
-      </c>
-      <c r="E266" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D267" s="2">
-        <v>6846</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D268" s="2">
-        <v>6801</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D269" s="2">
-        <v>6361</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D270" s="2">
-        <v>7794</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D271" s="2">
-        <v>8748</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D272" s="2">
-        <v>10006</v>
-      </c>
-      <c r="E272" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D273" s="2">
-        <v>6134</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D274" s="2">
-        <v>2700</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D275" s="2">
-        <v>11205</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D276" s="2">
-        <v>7098</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D277" s="2">
-        <v>7211</v>
-      </c>
-      <c r="E277" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A278" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D278" s="2">
-        <v>7884</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A279" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D279" s="2">
-        <v>8366</v>
-      </c>
-      <c r="E279" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D280" s="2">
-        <v>5639</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D281" s="2">
-        <v>7183</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D282" s="2">
-        <v>7903</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D283" s="2">
-        <v>8576</v>
-      </c>
-      <c r="E283" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D284" s="2">
-        <v>7352</v>
-      </c>
-      <c r="E284" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D285" s="2">
-        <v>8372</v>
-      </c>
-      <c r="E285" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D286" s="2">
-        <v>5751</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C287" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D287" s="2">
-        <v>818</v>
-      </c>
-      <c r="E287" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D288" s="2">
-        <v>6753</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D289" s="2">
-        <v>2896</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D290" s="2">
-        <v>8048</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D291" s="2">
-        <v>5654</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A292" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D292" s="2">
-        <v>2817</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A293" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D293" s="2">
-        <v>4606</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D294" s="2">
-        <v>8980</v>
-      </c>
-      <c r="E294" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D295" s="2">
-        <v>9910</v>
-      </c>
-      <c r="E295" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D296" s="2">
-        <v>4954</v>
-      </c>
-      <c r="E296" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D297" s="2">
-        <v>10505</v>
-      </c>
-      <c r="E297" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D298" s="2">
-        <v>4400</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D299" s="2">
-        <v>10917</v>
-      </c>
-      <c r="E299" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D300" s="2">
-        <v>8308</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A301" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D301" s="2">
-        <v>8761</v>
-      </c>
-      <c r="E301" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A302" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D302" s="2">
-        <v>5783</v>
-      </c>
-      <c r="E302" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A303" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D303" s="2">
-        <v>8627</v>
-      </c>
-      <c r="E303" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A304" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D304" s="2">
-        <v>6631</v>
-      </c>
-      <c r="E304" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A305" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D305" s="2">
-        <v>4992</v>
-      </c>
-      <c r="E305" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A306" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D306" s="2">
-        <v>8755</v>
-      </c>
-      <c r="E306" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A307" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D307" s="2">
-        <v>8256</v>
-      </c>
-      <c r="E307" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A308" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D308" s="2">
-        <v>4743</v>
-      </c>
-      <c r="E308" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A309" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D309" s="2">
-        <v>556</v>
-      </c>
-      <c r="E309" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A310" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D310" s="2">
-        <v>6361</v>
-      </c>
-      <c r="E310" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D311" s="2">
-        <v>5487</v>
-      </c>
-      <c r="E311" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A312" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D312" s="2">
-        <v>169</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A313" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C313" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D313" s="2">
-        <v>4483</v>
-      </c>
-      <c r="E313" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A314" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D314" s="2">
-        <v>6858</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A315" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C315" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D315" s="2">
-        <v>6737</v>
-      </c>
-      <c r="E315" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A316" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D316" s="2">
-        <v>7637</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A317" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D317" s="2">
-        <v>2573</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A318" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C318" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D318" s="2">
-        <v>3517</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A319" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C319" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D319" s="2">
-        <v>6562</v>
-      </c>
-      <c r="E319" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A320" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D320" s="2">
-        <v>5132</v>
-      </c>
-      <c r="E320" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A321" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C321" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D321" s="2">
-        <v>9876</v>
-      </c>
-      <c r="E321" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A322" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C322" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D322" s="2">
-        <v>8354</v>
-      </c>
-      <c r="E322" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A323" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B323" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C323" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D323" s="2">
-        <v>7868</v>
-      </c>
-      <c r="E323" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A324" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C324" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D324" s="2">
-        <v>7031</v>
-      </c>
-      <c r="E324" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A325" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D325" s="2">
-        <v>359</v>
-      </c>
-      <c r="E325" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A326" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C326" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D326" s="2">
-        <v>2314</v>
-      </c>
-      <c r="E326" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A327" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C327" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D327" s="2">
-        <v>8410</v>
-      </c>
-      <c r="E327" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A328" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C328" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D328" s="2">
-        <v>2112</v>
-      </c>
-      <c r="E328" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A329" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B329" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C329" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D329" s="2">
-        <v>3258</v>
-      </c>
-      <c r="E329" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A330" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B330" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C330" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D330" s="2">
-        <v>5240</v>
-      </c>
-      <c r="E330" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A331" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B331" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C331" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D331" s="2">
-        <v>767</v>
-      </c>
-      <c r="E331" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A332" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C332" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D332" s="2">
-        <v>11991</v>
-      </c>
-      <c r="E332" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A333" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B333" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C333" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D333" s="2">
-        <v>5969</v>
-      </c>
-      <c r="E333" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A334" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B334" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C334" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D334" s="2">
-        <v>6933</v>
-      </c>
-      <c r="E334" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A335" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B335" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C335" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D335" s="2">
-        <v>2104</v>
-      </c>
-      <c r="E335" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A336" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B336" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C336" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D336" s="2">
-        <v>75</v>
-      </c>
-      <c r="E336" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A337" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B337" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C337" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D337" s="2">
-        <v>6112</v>
-      </c>
-      <c r="E337" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A338" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B338" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C338" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D338" s="2">
-        <v>7084</v>
-      </c>
-      <c r="E338" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A339" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B339" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C339" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D339" s="2">
-        <v>3333</v>
-      </c>
-      <c r="E339" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A340" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B340" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C340" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D340" s="2">
-        <v>5117</v>
-      </c>
-      <c r="E340" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A341" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C341" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D341" s="2">
-        <v>2630</v>
-      </c>
-      <c r="E341" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A342" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B342" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C342" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D342" s="2">
-        <v>4302</v>
-      </c>
-      <c r="E342" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A343" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B343" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C343" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D343" s="2">
-        <v>12123</v>
-      </c>
-      <c r="E343" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A344" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C344" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D344" s="2">
-        <v>6808</v>
-      </c>
-      <c r="E344" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A345" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B345" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C345" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D345" s="2">
-        <v>8128</v>
-      </c>
-      <c r="E345" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A346" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B346" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C346" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D346" s="2">
-        <v>348</v>
-      </c>
-      <c r="E346" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A347" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B347" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C347" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D347" s="2">
-        <v>3783</v>
-      </c>
-      <c r="E347" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A348" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C348" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D348" s="2">
-        <v>11578</v>
-      </c>
-      <c r="E348" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A349" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B349" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C349" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D349" s="2">
-        <v>7215</v>
-      </c>
-      <c r="E349" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
